--- a/examples/Tesla DCF.xlsx
+++ b/examples/Tesla DCF.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E50A63-A709-734E-BCC2-D4ABCDBF307A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93028A5-4857-CE4D-9100-F929A49D1BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="34200" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="34200" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DCF" sheetId="1" r:id="rId1"/>
@@ -84,9 +84,6 @@
     <t>Beta</t>
   </si>
   <si>
-    <t>Judgment: 5-year monthly regression against the S&amp;P 500 gives 1.77</t>
-  </si>
-  <si>
     <t>Equity risk premium</t>
   </si>
   <si>
@@ -313,6 +310,9 @@
   </si>
   <si>
     <t>Sources: Tesla FY2025 Form 10-K and 2026 10-Q filings via SEC EDGAR; analyst estimates and price from Yahoo Finance, 14 Oct 2026.</t>
+  </si>
+  <si>
+    <t>Judgment. 5-year monthly regression against the S&amp;P 500 gives 1.77. Blended toward 1: 0.67 × 1.77 + 0.33 = 1.52</t>
   </si>
 </sst>
 </file>
@@ -321,12 +321,12 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.0%;\(0.0%\);&quot;-&quot;"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="0.0&quot;x&quot;"/>
-    <numFmt numFmtId="171" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);&quot;-&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.0&quot;x&quot;"/>
+    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -390,27 +390,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -822,204 +822,204 @@
         <v>17</v>
       </c>
       <c r="C13" s="6">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="P13" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="7">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="P14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="5">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="8">
         <f>C12+C13*C14+C15</f>
-        <v>0.13290000000000002</v>
+        <v>0.1203</v>
       </c>
       <c r="P16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" s="5">
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="P17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18" s="5">
         <v>0.21</v>
       </c>
       <c r="P18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C19" s="9">
         <f>C11/(C11+C7*C8)</f>
         <v>6.2226797460450374E-3</v>
       </c>
       <c r="P19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20" s="10">
         <f>C16*(1-C19)+C17*(1-C18)*C19</f>
-        <v>0.13240237230070881</v>
+        <v>0.11988077806550894</v>
       </c>
       <c r="P20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" s="5">
         <v>0.2</v>
       </c>
       <c r="P21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" s="6">
         <v>1.5</v>
       </c>
       <c r="P22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="P23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" s="5">
         <v>0.12</v>
       </c>
       <c r="P24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="7">
         <v>0.1</v>
       </c>
       <c r="P25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="5">
         <v>0.2</v>
       </c>
       <c r="P26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.2">
       <c r="D30" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="F30" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="G30" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="H30" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="I30" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="I30" s="11" t="s">
+      <c r="J30" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="J30" s="11" t="s">
+      <c r="K30" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="K30" s="11" t="s">
+      <c r="L30" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="L30" s="11" t="s">
+      <c r="M30" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="M30" s="11" t="s">
+      <c r="N30" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N30" s="11" t="s">
+      <c r="O30" s="11" t="s">
         <v>56</v>
-      </c>
-      <c r="O30" s="11" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E31" s="7">
         <v>0.13</v>
@@ -1056,12 +1056,12 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="P31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D32" s="12">
         <f>C9</f>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D33" s="9">
         <f>4355/94827</f>
@@ -1155,12 +1155,12 @@
         <v>0.1</v>
       </c>
       <c r="P33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E34" s="12">
         <f t="shared" ref="E34:O34" si="1">E32*E33</f>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E35" s="12">
         <f t="shared" ref="E35:N35" si="2">E34*(1-$C$21)</f>
@@ -1258,7 +1258,7 @@
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E36" s="12">
         <f t="shared" ref="E36:N36" si="3">-MAX(0,E32-D32)/$C$22</f>
@@ -1305,12 +1305,12 @@
         <v>-4235.6498283092651</v>
       </c>
       <c r="P36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E37" s="13">
         <f t="shared" ref="E37:O37" si="4">E35+E36</f>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E38" s="9">
         <f>(DATE(2026,12,31)-$C$6)/365</f>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E39" s="14">
         <f>E38/2</f>
@@ -1440,147 +1440,147 @@
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E40" s="15">
         <f t="shared" ref="E40:N40" si="5">1/(1+$C$20)^E39</f>
-        <v>0.98680207642163542</v>
+        <v>0.98797516530148655</v>
       </c>
       <c r="F40" s="15">
         <f t="shared" si="5"/>
-        <v>0.91508139181737724</v>
+        <v>0.92237210567624928</v>
       </c>
       <c r="G40" s="15">
         <f t="shared" si="5"/>
-        <v>0.80808855067850205</v>
+        <v>0.82363419726657183</v>
       </c>
       <c r="H40" s="15">
         <f t="shared" si="5"/>
-        <v>0.71360549080862812</v>
+        <v>0.73546596512650586</v>
       </c>
       <c r="I40" s="15">
         <f t="shared" si="5"/>
-        <v>0.63016954773663303</v>
+        <v>0.65673594862209861</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="5"/>
-        <v>0.55648907415860827</v>
+        <v>0.58643380749560647</v>
       </c>
       <c r="K40" s="15">
         <f t="shared" si="5"/>
-        <v>0.49142344432570029</v>
+        <v>0.5236573561951986</v>
       </c>
       <c r="L40" s="15">
         <f t="shared" si="5"/>
-        <v>0.43396539635224551</v>
+        <v>0.46760098615119433</v>
       </c>
       <c r="M40" s="15">
         <f t="shared" si="5"/>
-        <v>0.38322543909066109</v>
+        <v>0.41754532742220285</v>
       </c>
       <c r="N40" s="15">
         <f t="shared" si="5"/>
-        <v>0.33841808218050595</v>
+        <v>0.37284801703934417</v>
       </c>
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E41" s="13">
         <f t="shared" ref="E41:N41" si="6">E37*E38*E40</f>
-        <v>-1190.7518349408092</v>
+        <v>-1192.1673748647793</v>
       </c>
       <c r="F41" s="13">
         <f t="shared" si="6"/>
-        <v>-4434.7052390113176</v>
+        <v>-4470.0377976614936</v>
       </c>
       <c r="G41" s="13">
         <f t="shared" si="6"/>
-        <v>-3501.8515982960944</v>
+        <v>-3569.2186551678565</v>
       </c>
       <c r="H41" s="13">
         <f t="shared" si="6"/>
-        <v>-1718.198186653128</v>
+        <v>-1770.8331899093287</v>
       </c>
       <c r="I41" s="13">
         <f t="shared" si="6"/>
-        <v>973.89718904109623</v>
+        <v>1014.954303333942</v>
       </c>
       <c r="J41" s="13">
         <f t="shared" si="6"/>
-        <v>2140.5129060263384</v>
+        <v>2255.694121888077</v>
       </c>
       <c r="K41" s="13">
         <f t="shared" si="6"/>
-        <v>3222.8601723608585</v>
+        <v>3434.2570683842887</v>
       </c>
       <c r="L41" s="13">
         <f t="shared" si="6"/>
-        <v>4164.3962341781744</v>
+        <v>4487.1683369091697</v>
       </c>
       <c r="M41" s="13">
         <f t="shared" si="6"/>
-        <v>4408.6077427640703</v>
+        <v>4803.4221522360858</v>
       </c>
       <c r="N41" s="13">
         <f t="shared" si="6"/>
-        <v>4561.1278684748586</v>
+        <v>5025.1673027231127</v>
       </c>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D44" s="12">
         <f>SUM(E41:N41)</f>
-        <v>8625.895253944047</v>
+        <v>10018.406267871218</v>
       </c>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D45" s="12">
         <f>O37/(C20-C23)</f>
-        <v>149861.39507710838</v>
+        <v>169638.88445837094</v>
       </c>
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D46" s="12">
         <f>D45/(1+C20)^(E38+9)</f>
-        <v>47658.782755039494</v>
+        <v>59768.361528158421</v>
       </c>
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D47" s="13">
         <f>D44+D46</f>
-        <v>56284.678008983537</v>
+        <v>69786.767796029642</v>
       </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D48" s="9">
         <f>D46/D47</f>
-        <v>0.84674523228919829</v>
+        <v>0.8564426096197395</v>
       </c>
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D49" s="12">
         <f>C10</f>
@@ -1589,25 +1589,25 @@
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D50" s="13">
         <f>D47+D49</f>
-        <v>90728.678008983537</v>
+        <v>104230.76779602964</v>
       </c>
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D51" s="20">
         <f>D50/C8</f>
-        <v>22.972193444482475</v>
+        <v>26.390876768206013</v>
       </c>
     </row>
     <row r="52" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D52" s="21">
         <f>C7</f>
@@ -1616,42 +1616,42 @@
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D53" s="16">
         <f>D51/D52-1</f>
-        <v>-0.93743274473122762</v>
+        <v>-0.92812159067380429</v>
       </c>
     </row>
     <row r="54" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D54" s="17">
         <f>C7/1.08</f>
         <v>339.96296296296299</v>
       </c>
       <c r="P54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D55" s="17">
         <f>D51/1.08</f>
-        <v>21.270549485631921</v>
+        <v>24.435997007598157</v>
       </c>
     </row>
     <row r="58" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D59" s="18">
         <v>0.05</v>
@@ -1672,164 +1672,164 @@
     <row r="60" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C60" s="18">
         <f>$C$20+(-0.03)</f>
-        <v>0.10240237230070881</v>
+        <v>8.988077806550894E-2</v>
       </c>
       <c r="D60" s="21">
         <f t="shared" ref="D60:H64" si="7">(SUMPRODUCT($E$37:$H$37,$E$38:$H$38,1/(1+$C60)^$E$39:$H$39)+SUMPRODUCT($I$32:$N$32*($I$33:$N$33+D$59-$C$25)*(1-$C$21)+$I$36:$N$36,1/(1+$C60)^$I$39:$N$39)+$O$32*D$59*(1-$C$26)*(1-$C$23/$C$24)/($C60-$C$23)/(1+$C60)^($E$38+9)+$C$10)/$C$8</f>
-        <v>15.343606620807639</v>
+        <v>18.757977279144196</v>
       </c>
       <c r="E60" s="21">
         <f t="shared" si="7"/>
-        <v>24.299491497981744</v>
+        <v>29.719131405088223</v>
       </c>
       <c r="F60" s="21">
         <f t="shared" si="7"/>
-        <v>33.255376375155876</v>
+        <v>40.680285531032254</v>
       </c>
       <c r="G60" s="21">
         <f t="shared" si="7"/>
-        <v>42.211261252329976</v>
+        <v>51.641439656976296</v>
       </c>
       <c r="H60" s="21">
         <f t="shared" si="7"/>
-        <v>51.167146129504083</v>
+        <v>62.602593782920316</v>
       </c>
       <c r="P60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C61" s="18">
         <f>$C$20+(-0.015)</f>
-        <v>0.11740237230070881</v>
+        <v>0.10488077806550894</v>
       </c>
       <c r="D61" s="21">
         <f t="shared" si="7"/>
-        <v>12.640040999287601</v>
+        <v>14.812890375888903</v>
       </c>
       <c r="E61" s="21">
         <f t="shared" si="7"/>
-        <v>19.915633114471529</v>
+        <v>23.447070471542297</v>
       </c>
       <c r="F61" s="21">
         <f t="shared" si="7"/>
-        <v>27.19122522965548</v>
+        <v>32.081250567195703</v>
       </c>
       <c r="G61" s="21">
         <f t="shared" si="7"/>
-        <v>34.46681734483942</v>
+        <v>40.715430662849094</v>
       </c>
       <c r="H61" s="21">
         <f t="shared" si="7"/>
-        <v>41.742409460023346</v>
+        <v>49.3496107585025</v>
       </c>
     </row>
     <row r="62" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C62" s="18">
         <f>$C$20+(0)</f>
-        <v>0.13240237230070881</v>
+        <v>0.11988077806550894</v>
       </c>
       <c r="D62" s="21">
         <f t="shared" si="7"/>
-        <v>10.83099261652778</v>
+        <v>12.291363644391952</v>
       </c>
       <c r="E62" s="21">
         <f t="shared" si="7"/>
-        <v>16.901593030505126</v>
+        <v>19.341120206298978</v>
       </c>
       <c r="F62" s="21">
         <f t="shared" si="7"/>
-        <v>22.972193444482475</v>
+        <v>26.390876768206013</v>
       </c>
       <c r="G62" s="21">
         <f t="shared" si="7"/>
-        <v>29.042793858459824</v>
+        <v>33.44063333011303</v>
       </c>
       <c r="H62" s="21">
         <f t="shared" si="7"/>
-        <v>35.113394272437169</v>
+        <v>40.490389892020069</v>
       </c>
     </row>
     <row r="63" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C63" s="18">
         <f>$C$20+(0.015)</f>
-        <v>0.14740237230070879</v>
+        <v>0.13488077806550894</v>
       </c>
       <c r="D63" s="21">
         <f t="shared" si="7"/>
-        <v>9.5726709464564124</v>
+        <v>10.591555639176791</v>
       </c>
       <c r="E63" s="21">
         <f t="shared" si="7"/>
-        <v>14.738781527029886</v>
+        <v>16.495284629765827</v>
       </c>
       <c r="F63" s="21">
         <f t="shared" si="7"/>
-        <v>19.904892107603366</v>
+        <v>22.399013620354875</v>
       </c>
       <c r="G63" s="21">
         <f t="shared" si="7"/>
-        <v>25.071002688176844</v>
+        <v>28.30274261094392</v>
       </c>
       <c r="H63" s="21">
         <f t="shared" si="7"/>
-        <v>30.237113268750321</v>
+        <v>34.206471601532954</v>
       </c>
     </row>
     <row r="64" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C64" s="18">
         <f>$C$20+(0.03)</f>
-        <v>0.16240237230070881</v>
+        <v>0.14988077806550892</v>
       </c>
       <c r="D64" s="21">
         <f t="shared" si="7"/>
-        <v>8.6732315590896256</v>
+        <v>9.4030855793440384</v>
       </c>
       <c r="E64" s="21">
         <f t="shared" si="7"/>
-        <v>13.13687401741042</v>
+        <v>14.441149306733843</v>
       </c>
       <c r="F64" s="21">
         <f t="shared" si="7"/>
-        <v>17.600516475731226</v>
+        <v>19.479213034123653</v>
       </c>
       <c r="G64" s="21">
         <f t="shared" si="7"/>
-        <v>22.064158934052021</v>
+        <v>24.517276761513468</v>
       </c>
       <c r="H64" s="21">
         <f t="shared" si="7"/>
-        <v>26.527801392372819</v>
+        <v>29.555340488903273</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B66" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="71" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
